--- a/Entra Service Accounts/SharePoint/Service_Account_Inventory_SharePoint.xlsx
+++ b/Entra Service Accounts/SharePoint/Service_Account_Inventory_SharePoint.xlsx
@@ -112,11 +112,23 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">NEW until you categorise it. Filter on this to find what needs attention each run.</t>
+          <t xml:space="preserve">NEW on the run that adds the row. RENAMED when the display name or UPN changed since the last run - worth a look, because a repurposed account keeps its Object ID and therefore keeps your categorisation.</t>
         </r>
       </text>
     </comment>
     <comment ref="Q1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Prior name and UPN, recorded when a rename is detected. The row is matched on Object ID, so the categorisation carried over - check it is still correct.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="R1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -201,7 +213,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="181">
   <si>
     <t xml:space="preserve">Service Account Inventory - Dashboard</t>
   </si>
@@ -245,6 +257,12 @@
     <t xml:space="preserve">Filter Row Status on the tab to find them.</t>
   </si>
   <si>
+    <t xml:space="preserve">Renamed since last run</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same Object ID, different name. Your categorisation carried over automatically - confirm it is still correct, because a repurposed account keeps its identifier.</t>
+  </si>
+  <si>
     <t xml:space="preserve">CATEGORY BREAKDOWN</t>
   </si>
   <si>
@@ -347,6 +365,18 @@
     <t xml:space="preserve">Suggested Category is the runbook's heuristic guess, with a confidence rating. Treat it as a starting point - it is right often enough to be useful and wrong often enough to need checking, particularly for break-glass accounts, which depend entirely on your naming convention.</t>
   </si>
   <si>
+    <t xml:space="preserve">Renames</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rows are matched on Object ID, which does not change when an account is renamed. So a rename keeps the row and keeps your categorisation - which is the behaviour you want, and the reason the key is the Object ID rather than the UPN.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The runbook refreshes Display Name and User Principal Name on every run so the sheet stays searchable, records the old values in Previous Identifier, and sets Row Status to RENAMED. It never touches the green zone while doing so.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Give renamed rows a glance. An account that was repurposed - svc-oldapp becoming svc-newapp, say - keeps its Object ID and therefore inherits a categorisation made for a different purpose. That is the one case where a rename is more than cosmetic.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Editing while the runbook runs</t>
   </si>
   <si>
@@ -408,6 +438,9 @@
   </si>
   <si>
     <t xml:space="preserve">Row Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Previous Identifier</t>
   </si>
   <si>
     <t xml:space="preserve">Confirmed Category</t>
@@ -1324,9 +1357,9 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="tblUserCategorisation" displayName="tblUserCategorisation" ref="A1:X2" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:X2"/>
-  <tableColumns count="24">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="tblUserCategorisation" displayName="tblUserCategorisation" ref="A1:Y2" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:Y2"/>
+  <tableColumns count="25">
     <tableColumn id="1" name="Object ID"/>
     <tableColumn id="2" name="Display Name"/>
     <tableColumn id="3" name="User Principal Name"/>
@@ -1343,14 +1376,15 @@
     <tableColumn id="14" name="Confidence"/>
     <tableColumn id="15" name="First Seen"/>
     <tableColumn id="16" name="Row Status"/>
-    <tableColumn id="17" name="Confirmed Category"/>
-    <tableColumn id="18" name="Service Account?"/>
-    <tableColumn id="19" name="Owner Team"/>
-    <tableColumn id="20" name="Owner Name"/>
-    <tableColumn id="21" name="Environment"/>
-    <tableColumn id="22" name="Categorised By"/>
-    <tableColumn id="23" name="Categorised Date"/>
-    <tableColumn id="24" name="Notes"/>
+    <tableColumn id="17" name="Previous Identifier"/>
+    <tableColumn id="18" name="Confirmed Category"/>
+    <tableColumn id="19" name="Service Account?"/>
+    <tableColumn id="20" name="Owner Team"/>
+    <tableColumn id="21" name="Owner Name"/>
+    <tableColumn id="22" name="Environment"/>
+    <tableColumn id="23" name="Categorised By"/>
+    <tableColumn id="24" name="Categorised Date"/>
+    <tableColumn id="25" name="Notes"/>
   </tableColumns>
 </table>
 </file>
@@ -1536,7 +1570,7 @@
     <tabColor rgb="FFC00000"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:D36"/>
+  <dimension ref="B2:D37"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
@@ -1585,7 +1619,7 @@
         <v>7</v>
       </c>
       <c r="C7" s="6" t="n">
-        <f aca="false">COUNTIFS('User Categorisation'!$A$2:$A$5000,"&lt;&gt;",'User Categorisation'!$Q$2:$Q$5000,"")</f>
+        <f aca="false">COUNTIFS('User Categorisation'!$A$2:$A$5000,"&lt;&gt;",'User Categorisation'!$R$2:$R$5000,"")</f>
         <v>1</v>
       </c>
       <c r="D7" s="7" t="s">
@@ -1597,7 +1631,7 @@
         <v>9</v>
       </c>
       <c r="C8" s="6" t="n">
-        <f aca="false">COUNTIFS('User Categorisation'!$A$2:$A$5000,"&lt;&gt;",'User Categorisation'!$Q$2:$Q$5000,"&lt;&gt;")</f>
+        <f aca="false">COUNTIFS('User Categorisation'!$A$2:$A$5000,"&lt;&gt;",'User Categorisation'!$R$2:$R$5000,"&lt;&gt;")</f>
         <v>0</v>
       </c>
       <c r="D8" s="7"/>
@@ -1607,7 +1641,7 @@
         <v>10</v>
       </c>
       <c r="C9" s="9" t="n">
-        <f aca="false">IF(COUNTA('User Categorisation'!$A$2:$A$5000)=0,"n/a",COUNTIFS('User Categorisation'!$A$2:$A$5000,"&lt;&gt;",'User Categorisation'!$Q$2:$Q$5000,"&lt;&gt;")/COUNTA('User Categorisation'!$A$2:$A$5000))</f>
+        <f aca="false">IF(COUNTA('User Categorisation'!$A$2:$A$5000)=0,"n/a",COUNTIFS('User Categorisation'!$A$2:$A$5000,"&lt;&gt;",'User Categorisation'!$R$2:$R$5000,"&lt;&gt;")/COUNTA('User Categorisation'!$A$2:$A$5000))</f>
         <v>0</v>
       </c>
       <c r="D9" s="7" t="s">
@@ -1626,116 +1660,116 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="3" t="s">
+    <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C11" s="6" t="n">
+        <f aca="false">COUNTIF('User Categorisation'!$P$2:$P$5000,"RENAMED")</f>
+        <v>0</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D13" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C13" s="6" t="n">
-        <f aca="false">COUNTIF('User Categorisation'!$Q$2:$Q$5000,"Service Account")</f>
-        <v>0</v>
-      </c>
-      <c r="D13" s="7"/>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C14" s="6" t="n">
-        <f aca="false">COUNTIF('User Categorisation'!$Q$2:$Q$5000,"Privileged / Admin")</f>
+        <f aca="false">COUNTIF('User Categorisation'!$R$2:$R$5000,"Service Account")</f>
         <v>0</v>
       </c>
       <c r="D14" s="7"/>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C15" s="6" t="n">
-        <f aca="false">COUNTIF('User Categorisation'!$Q$2:$Q$5000,"Break-Glass (Emergency Access)")</f>
+        <f aca="false">COUNTIF('User Categorisation'!$R$2:$R$5000,"Privileged / Admin")</f>
         <v>0</v>
       </c>
       <c r="D15" s="7"/>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C16" s="6" t="n">
-        <f aca="false">COUNTIF('User Categorisation'!$Q$2:$Q$5000,"Shared / Departmental")</f>
+        <f aca="false">COUNTIF('User Categorisation'!$R$2:$R$5000,"Break-Glass (Emergency Access)")</f>
         <v>0</v>
       </c>
       <c r="D16" s="7"/>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C17" s="6" t="n">
-        <f aca="false">COUNTIF('User Categorisation'!$Q$2:$Q$5000,"Standard User")</f>
+        <f aca="false">COUNTIF('User Categorisation'!$R$2:$R$5000,"Shared / Departmental")</f>
         <v>0</v>
       </c>
       <c r="D17" s="7"/>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C18" s="6" t="n">
-        <f aca="false">COUNTIF('User Categorisation'!$Q$2:$Q$5000,"Decommission Candidate")</f>
+        <f aca="false">COUNTIF('User Categorisation'!$R$2:$R$5000,"Standard User")</f>
         <v>0</v>
       </c>
       <c r="D18" s="7"/>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C20" s="4" t="s">
+    <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C19" s="6" t="n">
+        <f aca="false">COUNTIF('User Categorisation'!$R$2:$R$5000,"Decommission Candidate")</f>
+        <v>0</v>
+      </c>
+      <c r="D19" s="7"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D21" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C21" s="6" t="n">
-        <f aca="false">COUNTIF('User Categorisation'!$R$2:$R$5000,"Yes")</f>
+    <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" s="6" t="n">
+        <f aca="false">COUNTIF('User Categorisation'!$S$2:$S$5000,"Yes")</f>
         <v>0</v>
       </c>
-      <c r="D21" s="7"/>
-    </row>
-    <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C22" s="6" t="n">
-        <f aca="false">COUNTIFS('User Categorisation'!$R$2:$R$5000,"Yes",'User Categorisation'!$S$2:$S$5000,"")</f>
-        <v>0</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>24</v>
-      </c>
+      <c r="D22" s="7"/>
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="8" t="s">
         <v>25</v>
       </c>
       <c r="C23" s="6" t="n">
-        <f aca="false">COUNTIFS('User Categorisation'!$R$2:$R$5000,"Yes",'User Categorisation'!$F$2:$F$5000,"")</f>
+        <f aca="false">COUNTIFS('User Categorisation'!$S$2:$S$5000,"Yes",'User Categorisation'!$T$2:$T$5000,"")</f>
         <v>0</v>
       </c>
       <c r="D23" s="7" t="s">
@@ -1747,105 +1781,117 @@
         <v>27</v>
       </c>
       <c r="C24" s="6" t="n">
-        <f aca="false">COUNTIFS('User Categorisation'!$R$2:$R$5000,"Yes",'User Categorisation'!$H$2:$H$5000,"No")</f>
+        <f aca="false">COUNTIFS('User Categorisation'!$S$2:$S$5000,"Yes",'User Categorisation'!$F$2:$F$5000,"")</f>
         <v>0</v>
       </c>
-      <c r="D24" s="7"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="3" t="s">
+      <c r="D24" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="C26" s="4" t="s">
+    </row>
+    <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B25" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C25" s="6" t="n">
+        <f aca="false">COUNTIFS('User Categorisation'!$S$2:$S$5000,"Yes",'User Categorisation'!$H$2:$H$5000,"No")</f>
+        <v>0</v>
+      </c>
+      <c r="D25" s="7"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C27" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="D27" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C27" s="6" t="n">
+    <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B28" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28" s="6" t="n">
         <f aca="false">COUNTA('Service Principals'!$A$2:$A$5000)</f>
         <v>1</v>
       </c>
-      <c r="D27" s="7"/>
-    </row>
-    <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C28" s="6" t="n">
+      <c r="D28" s="7"/>
+    </row>
+    <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B29" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C29" s="6" t="n">
         <f aca="false">COUNTIF('Service Principals'!$M$2:$M$5000,"High")</f>
         <v>1</v>
       </c>
-      <c r="D28" s="7"/>
-    </row>
-    <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C29" s="6" t="n">
+      <c r="D29" s="7"/>
+    </row>
+    <row r="30" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B30" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C30" s="6" t="n">
         <f aca="false">COUNTIFS('Service Principals'!$K$2:$K$5000,"&lt;=30",'Service Principals'!$K$2:$K$5000,"&gt;=0")</f>
         <v>1</v>
       </c>
-      <c r="D29" s="7"/>
-    </row>
-    <row r="30" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C30" s="6" t="n">
+      <c r="D30" s="7"/>
+    </row>
+    <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B31" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C31" s="6" t="n">
         <f aca="false">COUNTIF('Service Principals'!$O$2:$O$5000,"Yes")</f>
         <v>0</v>
       </c>
-      <c r="D30" s="7"/>
-    </row>
-    <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C31" s="6" t="n">
+      <c r="D31" s="7"/>
+    </row>
+    <row r="32" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B32" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C32" s="6" t="n">
         <f aca="false">COUNTIFS('Service Principals'!$A$2:$A$5000,"&lt;&gt;",'Service Principals'!$S$2:$S$5000,"")</f>
         <v>1</v>
       </c>
-      <c r="D31" s="7"/>
-    </row>
-    <row r="32" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C32" s="6" t="n">
+      <c r="D32" s="7"/>
+    </row>
+    <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B33" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C33" s="6" t="n">
         <f aca="false">COUNTA('Managed Identities'!$A$2:$A$5000)</f>
         <v>1</v>
       </c>
-      <c r="D32" s="7"/>
-    </row>
-    <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C33" s="6" t="n">
+      <c r="D33" s="7"/>
+    </row>
+    <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B34" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C34" s="6" t="n">
         <f aca="false">COUNTIF('Managed Identities'!$M$2:$M$5000,"Yes")</f>
         <v>0</v>
       </c>
-      <c r="D33" s="7"/>
-    </row>
-    <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C34" s="6" t="n">
+      <c r="D34" s="7"/>
+    </row>
+    <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B35" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C35" s="6" t="n">
         <f aca="false">COUNTIFS('Managed Identities'!$A$2:$A$5000,"&lt;&gt;",'Managed Identities'!$Q$2:$Q$5000,"")</f>
         <v>1</v>
       </c>
-      <c r="D34" s="7"/>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="2" t="s">
-        <v>36</v>
+      <c r="D35" s="7"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B37" s="2" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -1868,7 +1914,7 @@
     <tabColor rgb="FF1F3864"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:B32"/>
+  <dimension ref="B2:B40"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
@@ -1877,82 +1923,102 @@
   <sheetData>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="10" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="11" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="12" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="11" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="11" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="12" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="11" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="11" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="12" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="11" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="12" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="11" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="12" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B28" s="11" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="11" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="11" t="s">
-        <v>52</v>
+        <v>53</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B32" s="12" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B34" s="11" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B36" s="12" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B38" s="11" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B40" s="11" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -1972,7 +2038,7 @@
     <tabColor rgb="FF5B2C6F"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Z2"/>
+  <dimension ref="A1:AA2"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="38"/>
@@ -1990,102 +2056,106 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="24"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="15" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="0" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="0" width="38"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="H1" s="13" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="I1" s="13" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="K1" s="13" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="L1" s="13" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="M1" s="13" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="N1" s="13" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="O1" s="13" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="P1" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q1" s="14" t="s">
-        <v>69</v>
+        <v>74</v>
+      </c>
+      <c r="Q1" s="13" t="s">
+        <v>75</v>
       </c>
       <c r="R1" s="14" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="S1" s="14" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="T1" s="14" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="U1" s="14" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="V1" s="14" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="W1" s="14" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="X1" s="14" t="s">
-        <v>76</v>
+        <v>82</v>
+      </c>
+      <c r="Y1" s="14" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="15" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="E2" s="17" t="n">
         <v>45306</v>
@@ -2095,77 +2165,81 @@
         <v>46246</v>
       </c>
       <c r="H2" s="16" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="I2" s="16" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="J2" s="16" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="K2" s="16" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="L2" s="16" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="M2" s="16" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="N2" s="16" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="O2" s="17" t="n">
         <v>46248</v>
       </c>
       <c r="P2" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q2" s="16"/>
+        <v>91</v>
+      </c>
+      <c r="Q2" s="15"/>
       <c r="R2" s="16"/>
       <c r="S2" s="16"/>
       <c r="T2" s="16"/>
       <c r="U2" s="16"/>
       <c r="V2" s="16"/>
-      <c r="W2" s="17"/>
-      <c r="X2" s="15"/>
-      <c r="Z2" s="18" t="s">
-        <v>85</v>
+      <c r="W2" s="16"/>
+      <c r="X2" s="17"/>
+      <c r="Y2" s="15"/>
+      <c r="AA2" s="18" t="s">
+        <v>92</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:X5000">
+  <conditionalFormatting sqref="A2:Y5000">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
-      <formula>AND($A2&lt;&gt;"",$Q2="")</formula>
+      <formula>AND($A2&lt;&gt;"",$R2="")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:P5000">
     <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
       <formula>$P2="NEW"</formula>
     </cfRule>
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+      <formula>$P2="RENAMED"</formula>
+    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q5000">
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
-      <formula>AND($A2&lt;&gt;"",$Q2="")</formula>
+  <conditionalFormatting sqref="R2:R5000">
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+      <formula>AND($A2&lt;&gt;"",$R2="")</formula>
     </cfRule>
-    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
-      <formula>$Q2&lt;&gt;""</formula>
+    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+      <formula>$R2&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation allowBlank="true" errorStyle="warning" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="Q2:Q1002" type="list">
+    <dataValidation allowBlank="true" errorStyle="warning" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="R2:R1002" type="list">
       <formula1>Reference!$A$2:$A$12</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="warning" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="R2:R1002" type="list">
+    <dataValidation allowBlank="true" errorStyle="warning" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="S2:S1002" type="list">
       <formula1>Reference!$D$2:$D$4</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="warning" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="S2:S1002" type="list">
+    <dataValidation allowBlank="true" errorStyle="warning" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="T2:T1002" type="list">
       <formula1>Reference!$B$2:$B$14</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="warning" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="U2:U1002" type="list">
+    <dataValidation allowBlank="true" errorStyle="warning" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="V2:V1002" type="list">
       <formula1>Reference!$C$2:$C$7</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -2221,102 +2295,102 @@
   <sheetData>
     <row r="1" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="H1" s="13" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="I1" s="13" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="K1" s="13" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="L1" s="13" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="M1" s="13" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="N1" s="13" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="O1" s="13" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="P1" s="13" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="Q1" s="13" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="R1" s="13" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="S1" s="14" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="T1" s="14" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="U1" s="14" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="V1" s="14" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="W1" s="14" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="X1" s="14" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="Y1" s="14" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="Z1" s="14" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="15" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="E2" s="16" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="F2" s="16" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="G2" s="17" t="n">
         <v>45506</v>
@@ -2325,7 +2399,7 @@
         <v>46237</v>
       </c>
       <c r="I2" s="16" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="J2" s="17" t="n">
         <v>46277</v>
@@ -2334,23 +2408,23 @@
         <v>29</v>
       </c>
       <c r="L2" s="15" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M2" s="16" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="N2" s="16" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="O2" s="16" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="P2" s="15"/>
       <c r="Q2" s="17" t="n">
         <v>46248</v>
       </c>
       <c r="R2" s="16" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="S2" s="16"/>
       <c r="T2" s="16"/>
@@ -2432,81 +2506,81 @@
   <sheetData>
     <row r="1" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="H1" s="13" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="I1" s="13" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="K1" s="13" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="L1" s="13" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="M1" s="13" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="N1" s="13" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="O1" s="13" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="P1" s="13" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="Q1" s="14" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="R1" s="14" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="S1" s="14" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="T1" s="14" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="U1" s="14" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="15" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="E2" s="17" t="n">
         <v>45676</v>
@@ -2515,34 +2589,34 @@
         <v>46238</v>
       </c>
       <c r="G2" s="15" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="H2" s="16" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="I2" s="16" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="J2" s="16" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="K2" s="15" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="L2" s="16" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="M2" s="16" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="N2" s="16" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="O2" s="17" t="n">
         <v>46248</v>
       </c>
       <c r="P2" s="16" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="Q2" s="16"/>
       <c r="R2" s="16"/>
@@ -2600,40 +2674,40 @@
   <sheetData>
     <row r="1" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="H1" s="13" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="15" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="C2" s="15"/>
       <c r="D2" s="16" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="E2" s="16"/>
       <c r="F2" s="16"/>
@@ -2641,10 +2715,10 @@
         <v>46248</v>
       </c>
       <c r="H2" s="15" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="J2" s="18" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -2681,36 +2755,36 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="19" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="B1" s="19" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="C1" s="19" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="D1" s="19" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="E1" s="19" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="F1" s="19" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="G1" s="19" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="H1" s="19" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="20" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="C2" s="20" t="n">
         <v>0</v>
@@ -2725,10 +2799,10 @@
         <v>0</v>
       </c>
       <c r="G2" s="20" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="H2" s="20" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
     </row>
   </sheetData>
@@ -2764,146 +2838,146 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="21" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="B1" s="21" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="C1" s="21" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="D1" s="21" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="8" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="8" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="22" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
     </row>
   </sheetData>
